--- a/artfynd/A 58854-2021 artfynd.xlsx
+++ b/artfynd/A 58854-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58854-2021 artfynd.xlsx
+++ b/artfynd/A 58854-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2540,363 +2540,6 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>113266140</v>
-      </c>
-      <c r="B16" t="n">
-        <v>90330</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1110</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tallharticka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Pelloporus triqueter</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bottorp 3:1, Sm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>571880</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6272179</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fruktkropp vid roten av stubbe. Möjligtvis återfynd på mycel som hittades 2021. Svårt att känna igen stubben efter avverkning/markberedning</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>113266602</v>
-      </c>
-      <c r="B17" t="n">
-        <v>90330</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1110</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tallharticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Pelloporus triqueter</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bottorp 3:1, Sm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>571895</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6272121</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Återfynd ny fruktkropp. Första fynd 2021. Avverkades i april 2022</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>113266179</v>
-      </c>
-      <c r="B18" t="n">
-        <v>90330</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1110</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tallharticka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Pelloporus triqueter</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Vassmolösa, Sm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>572010</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6272147</v>
-      </c>
-      <c r="S18" t="n">
-        <v>25</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>återfynd ny fruktkropp. Första fynd 2022</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58854-2021 artfynd.xlsx
+++ b/artfynd/A 58854-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2540,6 +2540,125 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134020682</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56882</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vassmolösa, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>572021</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6272091</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lucia Caroli</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58854-2021 artfynd.xlsx
+++ b/artfynd/A 58854-2021 artfynd.xlsx
@@ -2545,7 +2545,7 @@
         <v>134020682</v>
       </c>
       <c r="B16" t="n">
-        <v>56882</v>
+        <v>56889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2021 artfynd.xlsx
+++ b/artfynd/A 58854-2021 artfynd.xlsx
@@ -2545,7 +2545,7 @@
         <v>134020682</v>
       </c>
       <c r="B16" t="n">
-        <v>56889</v>
+        <v>56899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 58854-2021 artfynd.xlsx
+++ b/artfynd/A 58854-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91655149</v>
+        <v>89246599</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Robacka, Sm</t>
+          <t>Vassmolösa, Karlskronavägen 500m S Plankvägen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571988.1786764015</v>
+        <v>571864</v>
       </c>
       <c r="R2" t="n">
-        <v>6272087.062945522</v>
+        <v>6272112</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,27 +746,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Ljungby</t>
+          <t>Hagby</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På stammen av tall som dog 2018. Fruktkropp ca 7 cm bred, taktegellagda, Krokformade seta i hymeniet 50-80 µm långa. Första för Kalmar läns fastland?</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,12 +786,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Gammal, spillkråkehackad tall.</t>
+          <t>Tall som dog 2018. Kring 100 år gammal, stående i västvänd, torr vägkant.</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Gammal, spillkråkehackad tall.</t>
+          <t>Pinus sylvestris # Tall som dog 2018. Kring 100 år gammal, stående i västvänd, torr vägkant.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,74 +809,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91655176</v>
+        <v>97157245</v>
       </c>
       <c r="B3" t="n">
-        <v>12274</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102016</v>
+        <v>1110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Robacka, Sm</t>
+          <t>Bottorp 3:1, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571966.4438276541</v>
+        <v>571895</v>
       </c>
       <c r="R3" t="n">
-        <v>6272131.850640122</v>
+        <v>6272121</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,22 +885,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan A 58854-2021</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,80 +904,77 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Under bark på död ved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Under bark of dead wood # Under tunng bark på liggande tallåga med violtagging (Trichaptum fuscoviolaceum) # Pinus sylvestris</t>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>97157245</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97157331</v>
+        <v>97157300</v>
       </c>
       <c r="B4" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>1110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1008,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571869.914339687</v>
+        <v>571880</v>
       </c>
       <c r="R4" t="n">
-        <v>6272194.08599331</v>
+        <v>6272179</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,21 +1016,11 @@
           <t>2021-11-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>avverkningsanmälan A 58854-2021</t>
@@ -1067,9 +1032,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>97157300</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1086,65 +1065,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97157200</v>
+        <v>104566089</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1110</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bottorp 3:1, Sm</t>
+          <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571974.5091949886</v>
+        <v>572010</v>
       </c>
       <c r="R5" t="n">
-        <v>6272176.596011261</v>
+        <v>6272147</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1168,27 +1141,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>avverkningsanmälan A 58854-2021</t>
+          <t>Fruktkropp vid grov stubbe. Avverkades av Södra april 2022</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1216,62 +1179,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97157182</v>
+        <v>113265967</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1110</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bottorp 3:1, Sm</t>
+          <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571999.0335560017</v>
+        <v>571906</v>
       </c>
       <c r="R6" t="n">
-        <v>6272194.637513769</v>
+        <v>6272134</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1298,27 +1255,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>avverkningsanmälan A 58854-2021</t>
+          <t>fruktkropp intill stubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,37 +1293,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97157346</v>
+        <v>97157331</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1389,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571851.1481389969</v>
+        <v>571870</v>
       </c>
       <c r="R7" t="n">
-        <v>6272194.316751301</v>
+        <v>6272194</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1422,24 +1364,14 @@
           <t>2021-11-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-13</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>avverkningsanmälan A 58854-2021. Två fruktkroppar</t>
+          <t>avverkningsanmälan A 58854-2021</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,37 +1399,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97157204</v>
+        <v>91655149</v>
       </c>
       <c r="B8" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1506,17 +1433,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bottorp 3:1, Sm</t>
+          <t>N Robacka, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571927.2531783797</v>
+        <v>571988</v>
       </c>
       <c r="R8" t="n">
-        <v>6272164.775138491</v>
+        <v>6272087</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1540,27 +1467,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 58854-2021</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,66 +1485,72 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Gammal, spillkråkehackad tall.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal, spillkråkehackad tall.</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97157224</v>
+        <v>97157346</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1640,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571920.0976126697</v>
+        <v>571851</v>
       </c>
       <c r="R9" t="n">
-        <v>6272196.043398901</v>
+        <v>6272194</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,24 +1591,14 @@
           <t>2021-11-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-11-13</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>avverkningsanmälan A 58854-2021</t>
+          <t>avverkningsanmälan A 58854-2021. Två fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1718,49 +1626,36 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97157245</v>
+        <v>97157204</v>
       </c>
       <c r="B10" t="n">
-        <v>89390</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1110</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1769,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571894.8757682361</v>
+        <v>571928</v>
       </c>
       <c r="R10" t="n">
-        <v>6272121.817859869</v>
+        <v>6272165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1802,21 +1697,11 @@
           <t>2021-11-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-11-13</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>avverkningsanmälan A 58854-2021</t>
@@ -1828,23 +1713,9 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>97157245</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1861,37 +1732,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97157300</v>
+        <v>134020682</v>
       </c>
       <c r="B11" t="n">
-        <v>89390</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1110</v>
+        <v>100070</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1901,24 +1767,30 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bottorp 3:1, Sm</t>
+          <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571880.1166957233</v>
+        <v>572021</v>
       </c>
       <c r="R11" t="n">
-        <v>6272178.289463171</v>
+        <v>6272091</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1942,27 +1814,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-11-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 58854-2021</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1971,70 +1828,55 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>97157300</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lucia Caroli</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104566089</v>
+        <v>134020683</v>
       </c>
       <c r="B12" t="n">
-        <v>89390</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1110</v>
+        <v>100070</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2044,24 +1886,25 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kalmar, Sm</t>
+          <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572009.781937201</v>
+        <v>572045</v>
       </c>
       <c r="R12" t="n">
-        <v>6272146.909375641</v>
+        <v>6272094</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2080,32 +1923,17 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Ljungby</t>
+          <t>Hagby</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fruktkropp vid grov stubbe. Avverkades av Södra april 2022</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2121,49 +1949,43 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lucia Caroli</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110281010</v>
+        <v>110287255</v>
       </c>
       <c r="B13" t="n">
-        <v>8721</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102341</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Jätteknäppare</t>
-        </is>
+        <v>101517</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Stenagostus rufus</t>
+          <t>Pediacus depressus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(De Geer, 1774)</t>
+          <t>(Herbst, 1797)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2178,7 +2000,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>larv/nymf</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2190,10 +2012,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571966.4438276541</v>
+        <v>571966</v>
       </c>
       <c r="R13" t="n">
-        <v>6272131.850640122</v>
+        <v>6272132</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2223,24 +2045,14 @@
           <t>2023-06-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-22</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Sannolikt ettårig larv, ca 20 mm. Under bark på stubbe i kanten på hygge från 2022.</t>
+          <t>Under bark på tallstubbe, nära marken. Stubben ca 1 år gammal, avverkad 2022.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2252,6 +2064,31 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Hyggeskant</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stump # Avverkningsstubbe på sandmark # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2268,15 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110287255</v>
+        <v>91655176</v>
       </c>
       <c r="B14" t="n">
-        <v>6603</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2284,21 +2116,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101517</v>
+        <v>102016</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gropig brunbagge</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pediacus depressus</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Herbst, 1797)</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2312,7 +2149,11 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2320,10 +2161,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>571966.4438276541</v>
+        <v>571966</v>
       </c>
       <c r="R14" t="n">
-        <v>6272131.850640122</v>
+        <v>6272132</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2350,27 +2191,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Under bark på tallstubbe, nära marken. Stubben ca 1 år gammal, avverkad 2022.</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2383,11 +2209,6 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Hyggeskant</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>tall</t>
@@ -2400,12 +2221,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Under bark på död ved</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stump # Avverkningsstubbe på sandmark # Pinus sylvestris</t>
+          <t>Under bark of dead wood # Under tunng bark på liggande tallåga med violtagging (Trichaptum fuscoviolaceum) # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2423,37 +2244,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113265967</v>
+        <v>110281010</v>
       </c>
       <c r="B15" t="n">
-        <v>90330</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1110</v>
+        <v>102341</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Jätteknäppare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Stenagostus rufus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(De Geer, 1774)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2463,24 +2279,30 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vassmolösa, Sm</t>
+          <t>N Robacka, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>571906</v>
+        <v>571966</v>
       </c>
       <c r="R15" t="n">
-        <v>6272134</v>
+        <v>6272132</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2504,17 +2326,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023-06-22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>fruktkropp intill stubbe</t>
+          <t>Sannolikt ettårig larv, ca 20 mm. Under bark på stubbe i kanten på hygge från 2022.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2530,22 +2352,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134020682</v>
+        <v>97157182</v>
       </c>
       <c r="B16" t="n">
-        <v>56899</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,54 +2375,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100070</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vassmolösa, Sm</t>
+          <t>Bottorp 3:1, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572021</v>
+        <v>571999</v>
       </c>
       <c r="R16" t="n">
-        <v>6272091</v>
+        <v>6272195</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2624,12 +2441,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2021-11-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2021-11-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan A 58854-2021</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2645,19 +2467,245 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lucia Caroli</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>97157200</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bottorp 3:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>571974</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6272176</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-11-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-11-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan A 58854-2021</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>97157224</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bottorp 3:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>571920</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6272196</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-11-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-11-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan A 58854-2021</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58854-2021 artfynd.xlsx
+++ b/artfynd/A 58854-2021 artfynd.xlsx
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+          <t>Lucia Caroli, Tyra Westelius, Tobias Uller</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 58854-2021 artfynd.xlsx
+++ b/artfynd/A 58854-2021 artfynd.xlsx
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lucia Caroli, Tyra Westelius, Tobias Uller</t>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 58854-2021 artfynd.xlsx
+++ b/artfynd/A 58854-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89246599</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157245</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157300</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104566089</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1290,6 +1315,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113265967</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1396,6 +1426,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157331</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1517,6 +1552,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91655149</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1623,6 +1663,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157346</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1729,6 +1774,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157204</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1848,6 +1898,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020682</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1962,6 +2017,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020683</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2102,6 +2162,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110287255</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2241,6 +2306,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91655176</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2361,6 +2431,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110281010</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2476,6 +2551,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157182</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2591,6 +2671,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157200</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2706,8 +2791,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157224</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>